--- a/Deliverables/BOM/eSpark-BOM(5)-v2.0 Boards).xlsx
+++ b/Deliverables/BOM/eSpark-BOM(5)-v2.0 Boards).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8958397C-2D57-4540-9755-5D9C4E1F2A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F56C9F6-632C-44BA-9141-00182E4862D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="258">
   <si>
     <t>S. No.</t>
   </si>
@@ -518,9 +518,6 @@
     <t>C3, C5, C7, C9, C11, C13, C15, C17, C27, C29, C53, C55, C70, C72, C76, C78, C85, C#1, C#2</t>
   </si>
   <si>
-    <t>C21, C22, C23, C24, C25, C26, C28, C30, C31, C32, C33, C34, C35, C37, C38, C39, C40, C41, C42, C54, C58, C59, C71, C77, C79, C81, C82, C84</t>
-  </si>
-  <si>
     <t>CAP CER 22PF 50V C0G/NP0 0402</t>
   </si>
   <si>
@@ -588,9 +585,6 @@
   </si>
   <si>
     <t>20K</t>
-  </si>
-  <si>
-    <t>SB1, SB2, SB3, SB4, SB5, SB8, SB9, SB10, SB11, SB12, SB13, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB21, SB22, SB23, SB24, SB25, SB26, SB27, SB28, SB29, SB30, SB32, SB34, SB35, SB36, SB37, SB38, SB40, SB41, SB42, SB44, SB45, SB46, SB47, SB48, SB49, SB50, SB70, SB71, SB72</t>
   </si>
   <si>
     <t>IC RF TXRX+MCU BLUETOOTH WIFI</t>
@@ -713,6 +707,108 @@
   </si>
   <si>
     <t>C71947</t>
+  </si>
+  <si>
+    <t>C21, C22, C23, C24, C25, C26, C28, C30, C31, C32, C33, C34, C35, C37, C38, C39, C40, C41, C42, C54, C58, C59, C71, C77, C79, C81, C82, C84, C87</t>
+  </si>
+  <si>
+    <t>CAP SMD 4700pF ±10% 25V X7R 0603</t>
+  </si>
+  <si>
+    <t>C86</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R8BB472</t>
+  </si>
+  <si>
+    <t>CAP CER 33000pF ±10% 25V X7R 0603</t>
+  </si>
+  <si>
+    <t>C88, C89</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R8BB333</t>
+  </si>
+  <si>
+    <t>DIODE TVS SMD 5.5V 5A 90W</t>
+  </si>
+  <si>
+    <t>D2, D3</t>
+  </si>
+  <si>
+    <t>TPD1E10B06DPYR</t>
+  </si>
+  <si>
+    <t>C505480</t>
+  </si>
+  <si>
+    <t>4.7nF</t>
+  </si>
+  <si>
+    <t>C113810</t>
+  </si>
+  <si>
+    <t>33nF</t>
+  </si>
+  <si>
+    <t>C48260</t>
+  </si>
+  <si>
+    <t>FIXED IND 3.3NH 1A 120 MOHM SMD</t>
+  </si>
+  <si>
+    <t>L2, L3</t>
+  </si>
+  <si>
+    <t>LQG18HN3N3S00D</t>
+  </si>
+  <si>
+    <t>FIXED IND 1.2NH 1A 90 MOHM SMD</t>
+  </si>
+  <si>
+    <t>L4, L5</t>
+  </si>
+  <si>
+    <t>IND 0402</t>
+  </si>
+  <si>
+    <t>LQG15HS1N2S02D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murata </t>
+  </si>
+  <si>
+    <t>C162552</t>
+  </si>
+  <si>
+    <t>C77105</t>
+  </si>
+  <si>
+    <t>RES SMD 0R, 1%, 0.1W, 0603</t>
+  </si>
+  <si>
+    <t>R6, R7, R8, R9</t>
+  </si>
+  <si>
+    <t>RC0603FR-070RL</t>
+  </si>
+  <si>
+    <t>C100044</t>
+  </si>
+  <si>
+    <t>0R</t>
+  </si>
+  <si>
+    <t>SB1, SB2, SB3, SB4, SB5, SB6, SB7, SB8, SB9, SB10, SB11, SB12, SB13, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB21, SB22, SB23, SB24, SB25, SB26, SB27, SB28, SB29, SB30, SB31, SB32, SB33, SB34, SB35, SB36, SB37, SB38, SB39, SB40, SB41, SB42, SB43, SB44, SB45, SB46, SB47, SB48, SB49, SB50, SB70, SB71, SB72</t>
+  </si>
+  <si>
+    <t>5V Adaptor</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>Aliexpress Shipping</t>
   </si>
 </sst>
 </file>
@@ -724,7 +820,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -902,11 +998,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -953,7 +1056,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1239,55 +1342,51 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
+      <left style="medium">
         <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom style="medium">
         <color indexed="64"/>
@@ -1299,33 +1398,9 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1334,9 +1409,54 @@
         <color auto="1"/>
       </left>
       <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1346,8 +1466,8 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
@@ -1359,48 +1479,13 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1412,7 +1497,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1495,13 +1580,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1514,9 +1596,6 @@
     <xf numFmtId="165" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1587,34 +1666,7 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1704,12 +1756,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1749,9 +1795,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1773,19 +1816,139 @@
     <xf numFmtId="165" fontId="9" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1800,275 +1963,170 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="4" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2347,7 +2405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
@@ -2372,26 +2430,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" thickBot="1">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="156" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="132"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="157"/>
+      <c r="M1" s="157"/>
+      <c r="N1" s="157"/>
+      <c r="O1" s="157"/>
+      <c r="P1" s="157"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="158"/>
     </row>
     <row r="2" spans="1:19" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2453,52 +2511,52 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="135" t="s">
+      <c r="B3" s="198" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="89" t="s">
+      <c r="C3" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="138" t="s">
-        <v>166</v>
-      </c>
-      <c r="E3" s="91" t="s">
+      <c r="D3" s="208" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="91" t="s">
+      <c r="F3" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="I3" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="90" t="s">
+      <c r="J3" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="46">
+      <c r="K3" s="44">
         <v>40</v>
       </c>
-      <c r="L3" s="92">
+      <c r="L3" s="81">
         <v>4</v>
       </c>
-      <c r="M3" s="47">
+      <c r="M3" s="45">
         <f>L3*5</f>
         <v>20</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="N3" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="48">
-        <v>2.58E-2</v>
-      </c>
-      <c r="P3" s="49">
+      <c r="O3" s="46">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="P3" s="47">
         <f>O3*K3</f>
-        <v>1.032</v>
+        <v>0.54399999999999993</v>
       </c>
       <c r="Q3" s="12"/>
       <c r="R3" s="13"/>
@@ -2507,49 +2565,49 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="136"/>
-      <c r="C4" s="94" t="s">
+      <c r="B4" s="199"/>
+      <c r="C4" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="139" t="s">
+      <c r="D4" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="96" t="s">
+      <c r="E4" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="96" t="s">
+      <c r="F4" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="57" t="s">
+      <c r="G4" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="I4" s="52" t="s">
+      <c r="I4" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="95" t="s">
+      <c r="J4" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="53">
+      <c r="K4" s="51">
         <v>20</v>
       </c>
-      <c r="L4" s="97">
+      <c r="L4" s="86">
         <v>1</v>
       </c>
-      <c r="M4" s="176">
-        <f t="shared" ref="M4:M36" si="0">L4*5</f>
+      <c r="M4" s="119">
+        <f t="shared" ref="M4:M41" si="0">L4*5</f>
         <v>5</v>
       </c>
-      <c r="N4" s="98" t="s">
+      <c r="N4" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="55">
+      <c r="O4" s="53">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="P4" s="177">
-        <f t="shared" ref="P4:P34" si="1">O4*K4</f>
+      <c r="P4" s="120">
+        <f t="shared" ref="P4:P40" si="1">O4*K4</f>
         <v>0.40599999999999997</v>
       </c>
       <c r="Q4" s="14"/>
@@ -2559,48 +2617,48 @@
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="136"/>
-      <c r="C5" s="94" t="s">
+      <c r="B5" s="199"/>
+      <c r="C5" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="140" t="s">
+      <c r="D5" s="207" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="95" t="s">
+      <c r="E5" s="84" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="95" t="s">
+      <c r="F5" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="G5" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="I5" s="52" t="s">
+      <c r="I5" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="95" t="s">
+      <c r="J5" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="53">
+      <c r="K5" s="51">
         <v>100</v>
       </c>
-      <c r="L5" s="97">
+      <c r="L5" s="86">
         <v>19</v>
       </c>
-      <c r="M5" s="176">
+      <c r="M5" s="119">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="N5" s="98" t="s">
+      <c r="N5" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="55">
+      <c r="O5" s="53">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="P5" s="177">
+      <c r="P5" s="120">
         <f t="shared" si="1"/>
         <v>0.73</v>
       </c>
@@ -2612,48 +2670,48 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="136"/>
-      <c r="C6" s="94" t="s">
+      <c r="B6" s="199"/>
+      <c r="C6" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="139" t="s">
+      <c r="D6" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="96" t="s">
+      <c r="E6" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="96" t="s">
+      <c r="F6" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="I6" s="52" t="s">
+      <c r="I6" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="95" t="s">
+      <c r="J6" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="51">
         <v>100</v>
       </c>
-      <c r="L6" s="97">
+      <c r="L6" s="86">
         <v>8</v>
       </c>
-      <c r="M6" s="176">
+      <c r="M6" s="119">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="N6" s="99" t="s">
+      <c r="N6" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="53">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="P6" s="177">
+      <c r="P6" s="120">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
@@ -2665,48 +2723,48 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="136"/>
-      <c r="C7" s="94" t="s">
+      <c r="B7" s="199"/>
+      <c r="C7" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" s="113" t="s">
         <v>162</v>
       </c>
-      <c r="D7" s="139" t="s">
+      <c r="E7" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="E7" s="96" t="s">
+      <c r="F7" s="117" t="s">
         <v>164</v>
       </c>
-      <c r="F7" s="171" t="s">
-        <v>165</v>
-      </c>
-      <c r="G7" s="57" t="s">
+      <c r="G7" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="H7" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="I7" s="50" t="s">
+        <v>210</v>
+      </c>
+      <c r="J7" s="84" t="s">
         <v>202</v>
       </c>
-      <c r="H7" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="I7" s="52" t="s">
-        <v>212</v>
-      </c>
-      <c r="J7" s="95" t="s">
-        <v>204</v>
-      </c>
-      <c r="K7" s="53">
+      <c r="K7" s="51">
         <v>100</v>
       </c>
-      <c r="L7" s="97">
+      <c r="L7" s="86">
         <v>1</v>
       </c>
-      <c r="M7" s="176">
+      <c r="M7" s="119">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N7" s="169" t="s">
+      <c r="N7" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="55">
+      <c r="O7" s="53">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="P7" s="177">
+      <c r="P7" s="120">
         <f t="shared" si="1"/>
         <v>0.13</v>
       </c>
@@ -2718,48 +2776,48 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="136"/>
-      <c r="C8" s="94" t="s">
+      <c r="B8" s="199"/>
+      <c r="C8" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="140" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" s="95" t="s">
+      <c r="D8" s="207" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" s="84" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="95" t="s">
+      <c r="F8" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="57" t="s">
+      <c r="G8" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="H8" s="51" t="s">
+      <c r="H8" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="I8" s="52" t="s">
+      <c r="I8" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="95" t="s">
+      <c r="J8" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="53">
+      <c r="K8" s="51">
         <v>150</v>
       </c>
-      <c r="L8" s="97">
-        <v>28</v>
-      </c>
-      <c r="M8" s="176">
+      <c r="L8" s="86">
+        <v>29</v>
+      </c>
+      <c r="M8" s="119">
         <f t="shared" si="0"/>
-        <v>140</v>
-      </c>
-      <c r="N8" s="99" t="s">
+        <v>145</v>
+      </c>
+      <c r="N8" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="O8" s="55">
+      <c r="O8" s="53">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="P8" s="177">
+      <c r="P8" s="120">
         <f t="shared" si="1"/>
         <v>1.1850000000000001</v>
       </c>
@@ -2771,48 +2829,48 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="136"/>
-      <c r="C9" s="94" t="s">
+      <c r="B9" s="199"/>
+      <c r="C9" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="139" t="s">
+      <c r="D9" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="96" t="s">
+      <c r="E9" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="96" t="s">
+      <c r="F9" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="57" t="s">
+      <c r="G9" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="H9" s="58" t="s">
+      <c r="H9" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="I9" s="52" t="s">
+      <c r="I9" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="95" t="s">
+      <c r="J9" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="K9" s="57">
+      <c r="K9" s="55">
         <v>10</v>
       </c>
-      <c r="L9" s="97">
+      <c r="L9" s="86">
         <v>1</v>
       </c>
-      <c r="M9" s="176">
+      <c r="M9" s="119">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N9" s="99" t="s">
+      <c r="N9" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="55">
+      <c r="O9" s="53">
         <v>4.4299999999999999E-2</v>
       </c>
-      <c r="P9" s="177">
+      <c r="P9" s="120">
         <f t="shared" si="1"/>
         <v>0.443</v>
       </c>
@@ -2824,48 +2882,48 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="136"/>
-      <c r="C10" s="94" t="s">
+      <c r="B10" s="199"/>
+      <c r="C10" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="139" t="s">
+      <c r="D10" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="96" t="s">
+      <c r="E10" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="96" t="s">
+      <c r="F10" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="57" t="s">
+      <c r="G10" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="H10" s="51" t="s">
+      <c r="H10" s="49" t="s">
         <v>121</v>
       </c>
-      <c r="I10" s="52" t="s">
+      <c r="I10" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="95" t="s">
+      <c r="J10" s="84" t="s">
         <v>71</v>
       </c>
-      <c r="K10" s="57">
+      <c r="K10" s="55">
         <v>100</v>
       </c>
-      <c r="L10" s="97">
+      <c r="L10" s="86">
         <v>6</v>
       </c>
-      <c r="M10" s="176">
+      <c r="M10" s="119">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="N10" s="98" t="s">
+      <c r="N10" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="55">
+      <c r="O10" s="53">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="P10" s="177">
+      <c r="P10" s="120">
         <f t="shared" si="1"/>
         <v>0.32</v>
       </c>
@@ -2877,48 +2935,48 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="136"/>
-      <c r="C11" s="94" t="s">
+      <c r="B11" s="199"/>
+      <c r="C11" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="140" t="s">
+      <c r="D11" s="166" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="95" t="s">
+      <c r="E11" s="84" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="95" t="s">
+      <c r="F11" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="57" t="s">
+      <c r="G11" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="H11" s="51" t="s">
+      <c r="H11" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="I11" s="52" t="s">
+      <c r="I11" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="95" t="s">
+      <c r="J11" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="57">
+      <c r="K11" s="55">
         <v>100</v>
       </c>
-      <c r="L11" s="97">
+      <c r="L11" s="86">
         <v>16</v>
       </c>
-      <c r="M11" s="176">
+      <c r="M11" s="119">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="N11" s="98" t="s">
+      <c r="N11" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="O11" s="55">
+      <c r="O11" s="53">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="P11" s="177">
+      <c r="P11" s="120">
         <f t="shared" si="1"/>
         <v>1.73</v>
       </c>
@@ -2930,48 +2988,48 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="136"/>
-      <c r="C12" s="94" t="s">
+      <c r="B12" s="199"/>
+      <c r="C12" s="83" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" s="84" t="s">
         <v>167</v>
       </c>
-      <c r="D12" s="139" t="s">
+      <c r="E12" s="85" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="85" t="s">
         <v>168</v>
       </c>
-      <c r="E12" s="96" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="96" t="s">
-        <v>169</v>
-      </c>
-      <c r="G12" s="57" t="s">
+      <c r="G12" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="H12" s="51" t="s">
-        <v>205</v>
-      </c>
-      <c r="I12" s="52" t="s">
+      <c r="H12" s="49" t="s">
+        <v>203</v>
+      </c>
+      <c r="I12" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="95" t="s">
-        <v>206</v>
-      </c>
-      <c r="K12" s="57">
+      <c r="J12" s="84" t="s">
+        <v>204</v>
+      </c>
+      <c r="K12" s="55">
         <v>50</v>
       </c>
-      <c r="L12" s="97">
+      <c r="L12" s="86">
         <v>1</v>
       </c>
-      <c r="M12" s="176">
+      <c r="M12" s="119">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N12" s="178" t="s">
+      <c r="N12" s="121" t="s">
         <v>16</v>
       </c>
-      <c r="O12" s="55">
+      <c r="O12" s="53">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="P12" s="177">
+      <c r="P12" s="120">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
@@ -2983,918 +3041,912 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="190" t="s">
+      <c r="B13" s="199"/>
+      <c r="C13" s="83" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="166" t="s">
         <v>170</v>
       </c>
-      <c r="D13" s="152" t="s">
+      <c r="E13" s="84" t="s">
+        <v>163</v>
+      </c>
+      <c r="F13" s="102" t="s">
         <v>171</v>
       </c>
-      <c r="E13" s="107" t="s">
-        <v>164</v>
-      </c>
-      <c r="F13" s="186" t="s">
-        <v>172</v>
-      </c>
-      <c r="G13" s="79" t="s">
-        <v>202</v>
-      </c>
-      <c r="H13" s="80" t="s">
-        <v>207</v>
-      </c>
-      <c r="I13" s="81" t="s">
-        <v>213</v>
-      </c>
-      <c r="J13" s="107" t="s">
-        <v>208</v>
-      </c>
-      <c r="K13" s="79">
+      <c r="G13" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="H13" s="49" t="s">
+        <v>205</v>
+      </c>
+      <c r="I13" s="50" t="s">
+        <v>211</v>
+      </c>
+      <c r="J13" s="84" t="s">
+        <v>206</v>
+      </c>
+      <c r="K13" s="55">
         <v>100</v>
       </c>
-      <c r="L13" s="112">
+      <c r="L13" s="86">
         <v>1</v>
       </c>
-      <c r="M13" s="83">
+      <c r="M13" s="119">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N13" s="187" t="s">
+      <c r="N13" s="121" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="84">
+      <c r="O13" s="53">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="P13" s="188">
+      <c r="P13" s="120">
         <f t="shared" si="1"/>
         <v>0.11</v>
       </c>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="17"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="15"/>
       <c r="S13" s="11"/>
     </row>
-    <row r="14" spans="1:19" ht="26.25" thickBot="1">
+    <row r="14" spans="1:19" ht="15.75" thickBot="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="200" t="s">
-        <v>196</v>
-      </c>
-      <c r="C14" s="203" t="s">
-        <v>193</v>
-      </c>
-      <c r="D14" s="162" t="s">
-        <v>194</v>
-      </c>
-      <c r="E14" s="143" t="s">
-        <v>209</v>
-      </c>
-      <c r="F14" s="143" t="s">
-        <v>195</v>
-      </c>
-      <c r="G14" s="144" t="s">
-        <v>211</v>
-      </c>
-      <c r="H14" s="145" t="s">
-        <v>210</v>
-      </c>
-      <c r="I14" s="146" t="s">
+      <c r="B14" s="199"/>
+      <c r="C14" s="83" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14" s="84" t="s">
+        <v>226</v>
+      </c>
+      <c r="E14" s="85" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="85" t="s">
+        <v>227</v>
+      </c>
+      <c r="G14" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>234</v>
+      </c>
+      <c r="I14" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="143" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" s="144">
-        <v>10</v>
-      </c>
-      <c r="L14" s="147">
+      <c r="J14" s="84" t="s">
+        <v>235</v>
+      </c>
+      <c r="K14" s="55">
+        <v>100</v>
+      </c>
+      <c r="L14" s="86">
         <v>1</v>
       </c>
-      <c r="M14" s="62">
+      <c r="M14" s="119">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N14" s="170" t="s">
+      <c r="N14" s="121" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="148">
-        <v>6.2600000000000003E-2</v>
-      </c>
-      <c r="P14" s="64">
+      <c r="O14" s="53">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="P14" s="120">
         <f t="shared" si="1"/>
-        <v>0.626</v>
-      </c>
-      <c r="Q14" s="149"/>
-      <c r="R14" s="156"/>
+        <v>0.37</v>
+      </c>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="15"/>
       <c r="S14" s="11"/>
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="116" t="s">
-        <v>201</v>
-      </c>
-      <c r="C15" s="163" t="s">
-        <v>197</v>
-      </c>
-      <c r="D15" s="164" t="s">
-        <v>198</v>
-      </c>
-      <c r="E15" s="165" t="s">
-        <v>199</v>
-      </c>
-      <c r="F15" s="165" t="s">
-        <v>200</v>
-      </c>
-      <c r="G15" s="65" t="s">
-        <v>214</v>
-      </c>
-      <c r="H15" s="166" t="s">
-        <v>215</v>
-      </c>
-      <c r="I15" s="66" t="s">
+      <c r="B15" s="200"/>
+      <c r="C15" s="132" t="s">
+        <v>228</v>
+      </c>
+      <c r="D15" s="94" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="191" t="s">
+        <v>230</v>
+      </c>
+      <c r="G15" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="H15" s="69" t="s">
+        <v>236</v>
+      </c>
+      <c r="I15" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="J15" s="101" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" s="65">
+      <c r="J15" s="94" t="s">
+        <v>237</v>
+      </c>
+      <c r="K15" s="68">
         <v>50</v>
       </c>
-      <c r="L15" s="167">
-        <v>1</v>
-      </c>
-      <c r="M15" s="69">
+      <c r="L15" s="99">
+        <v>2</v>
+      </c>
+      <c r="M15" s="72">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N15" s="172" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="O15" s="70">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="P15" s="71">
+      <c r="O15" s="73">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="P15" s="130">
         <f t="shared" si="1"/>
-        <v>1.05</v>
-      </c>
-      <c r="Q15" s="168"/>
-      <c r="R15" s="204"/>
+        <v>0.255</v>
+      </c>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="17"/>
       <c r="S15" s="11"/>
     </row>
     <row r="16" spans="1:19" ht="26.25" thickBot="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" s="201" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="150" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="101" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" s="65" t="s">
-        <v>148</v>
-      </c>
-      <c r="H16" s="66" t="s">
-        <v>146</v>
-      </c>
-      <c r="I16" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="J16" s="68" t="s">
+      <c r="B16" s="201" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="195" t="s">
+        <v>191</v>
+      </c>
+      <c r="D16" s="125" t="s">
+        <v>192</v>
+      </c>
+      <c r="E16" s="125" t="s">
+        <v>207</v>
+      </c>
+      <c r="F16" s="125" t="s">
+        <v>193</v>
+      </c>
+      <c r="G16" s="48" t="s">
+        <v>209</v>
+      </c>
+      <c r="H16" s="126" t="s">
+        <v>208</v>
+      </c>
+      <c r="I16" s="183" t="s">
+        <v>39</v>
+      </c>
+      <c r="J16" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="68">
-        <v>42</v>
-      </c>
-      <c r="L16" s="69">
-        <v>8</v>
-      </c>
-      <c r="M16" s="69">
+      <c r="K16" s="48">
+        <v>10</v>
+      </c>
+      <c r="L16" s="184">
+        <v>1</v>
+      </c>
+      <c r="M16" s="52">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="N16" s="102" t="s">
-        <v>155</v>
-      </c>
-      <c r="O16" s="70">
-        <v>3.68</v>
-      </c>
-      <c r="P16" s="71">
+        <v>5</v>
+      </c>
+      <c r="N16" s="185" t="s">
+        <v>16</v>
+      </c>
+      <c r="O16" s="127">
+        <v>6.2600000000000003E-2</v>
+      </c>
+      <c r="P16" s="54">
         <f t="shared" si="1"/>
-        <v>154.56</v>
-      </c>
-      <c r="Q16" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="R16" s="202"/>
+        <v>0.626</v>
+      </c>
+      <c r="Q16" s="128"/>
+      <c r="R16" s="131"/>
       <c r="S16" s="11"/>
     </row>
-    <row r="17" spans="1:19" ht="26.25" thickBot="1">
+    <row r="17" spans="1:19" ht="15.75" thickBot="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="124" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="153" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="142" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="143" t="s">
+      <c r="B17" s="202"/>
+      <c r="C17" s="196" t="s">
+        <v>231</v>
+      </c>
+      <c r="D17" s="89" t="s">
+        <v>232</v>
+      </c>
+      <c r="E17" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="143" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="144" t="s">
-        <v>123</v>
-      </c>
-      <c r="H17" s="145" t="s">
-        <v>124</v>
-      </c>
-      <c r="I17" s="146" t="s">
+      <c r="F17" s="89" t="s">
+        <v>233</v>
+      </c>
+      <c r="G17" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="58" t="s">
+        <v>238</v>
+      </c>
+      <c r="I17" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="J17" s="154" t="s">
+      <c r="J17" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="K17" s="154">
+      <c r="K17" s="57">
+        <v>15</v>
+      </c>
+      <c r="L17" s="186">
+        <v>2</v>
+      </c>
+      <c r="M17" s="133">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L17" s="62">
+      <c r="N17" s="187" t="s">
+        <v>16</v>
+      </c>
+      <c r="O17" s="60">
+        <v>0.11219999999999999</v>
+      </c>
+      <c r="P17" s="134">
+        <f t="shared" si="1"/>
+        <v>1.6829999999999998</v>
+      </c>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="11"/>
+    </row>
+    <row r="18" spans="1:19" ht="15.75" thickBot="1">
+      <c r="A18" s="6">
+        <v>16</v>
+      </c>
+      <c r="B18" s="203" t="s">
+        <v>199</v>
+      </c>
+      <c r="C18" s="78" t="s">
+        <v>195</v>
+      </c>
+      <c r="D18" s="79" t="s">
+        <v>196</v>
+      </c>
+      <c r="E18" s="80" t="s">
+        <v>197</v>
+      </c>
+      <c r="F18" s="80" t="s">
+        <v>198</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="H18" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="41">
+        <v>50</v>
+      </c>
+      <c r="L18" s="81">
         <v>1</v>
       </c>
-      <c r="M17" s="62">
+      <c r="M18" s="45">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N17" s="155" t="s">
+      <c r="N18" s="192" t="s">
         <v>16</v>
       </c>
-      <c r="O17" s="148">
-        <v>6.0600000000000001E-2</v>
-      </c>
-      <c r="P17" s="64">
+      <c r="O18" s="46">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="P18" s="47">
         <f t="shared" si="1"/>
-        <v>0.60599999999999998</v>
-      </c>
-      <c r="Q17" s="149"/>
-      <c r="R17" s="156"/>
-      <c r="S17" s="11"/>
-    </row>
-    <row r="18" spans="1:19" ht="26.25" thickBot="1">
-      <c r="A18" s="6">
-        <v>16</v>
-      </c>
-      <c r="B18" s="135" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="103" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="151" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="104" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="G18" s="72" t="s">
-        <v>125</v>
-      </c>
-      <c r="H18" s="73" t="s">
-        <v>126</v>
-      </c>
-      <c r="I18" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="J18" s="75" t="s">
-        <v>22</v>
-      </c>
-      <c r="K18" s="75">
-        <v>7</v>
-      </c>
-      <c r="L18" s="76">
-        <v>1</v>
-      </c>
-      <c r="M18" s="76">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N18" s="105" t="s">
-        <v>16</v>
-      </c>
-      <c r="O18" s="77">
-        <v>0.25650000000000001</v>
-      </c>
-      <c r="P18" s="78">
-        <f>O18*K18</f>
-        <v>1.7955000000000001</v>
-      </c>
-      <c r="Q18" s="18"/>
-      <c r="R18" s="38"/>
+        <v>1.05</v>
+      </c>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="13"/>
       <c r="S18" s="11"/>
     </row>
-    <row r="19" spans="1:19" ht="26.25" thickBot="1">
+    <row r="19" spans="1:19" ht="15.75" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="136"/>
-      <c r="C19" s="110" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="140" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" s="95" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="95" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="57" t="s">
-        <v>127</v>
-      </c>
-      <c r="H19" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="I19" s="52" t="s">
+      <c r="B19" s="204"/>
+      <c r="C19" s="83" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" s="84" t="s">
+        <v>240</v>
+      </c>
+      <c r="E19" s="85" t="s">
+        <v>197</v>
+      </c>
+      <c r="F19" s="85" t="s">
+        <v>241</v>
+      </c>
+      <c r="G19" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="H19" s="49" t="s">
+        <v>247</v>
+      </c>
+      <c r="I19" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="K19" s="53">
-        <v>7</v>
-      </c>
-      <c r="L19" s="176">
+      <c r="J19" s="84" t="s">
+        <v>216</v>
+      </c>
+      <c r="K19" s="55">
+        <v>20</v>
+      </c>
+      <c r="L19" s="86">
         <v>2</v>
       </c>
-      <c r="M19" s="176">
+      <c r="M19" s="119">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N19" s="99" t="s">
+      <c r="N19" s="121" t="s">
         <v>16</v>
       </c>
-      <c r="O19" s="55">
-        <v>0.1215</v>
-      </c>
-      <c r="P19" s="177">
+      <c r="O19" s="53">
+        <v>7.4300000000000005E-2</v>
+      </c>
+      <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>0.85050000000000003</v>
+        <v>1.4860000000000002</v>
       </c>
       <c r="Q19" s="14"/>
       <c r="R19" s="15"/>
       <c r="S19" s="11"/>
     </row>
-    <row r="20" spans="1:19" ht="26.25" thickBot="1">
+    <row r="20" spans="1:19" ht="15.75" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="137"/>
-      <c r="C20" s="106" t="s">
-        <v>173</v>
-      </c>
-      <c r="D20" s="152" t="s">
-        <v>174</v>
-      </c>
-      <c r="E20" s="107" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="107" t="s">
-        <v>175</v>
-      </c>
-      <c r="G20" s="79" t="s">
+      <c r="B20" s="205"/>
+      <c r="C20" s="132" t="s">
+        <v>242</v>
+      </c>
+      <c r="D20" s="94" t="s">
+        <v>243</v>
+      </c>
+      <c r="E20" s="191" t="s">
+        <v>244</v>
+      </c>
+      <c r="F20" s="191" t="s">
+        <v>245</v>
+      </c>
+      <c r="G20" s="68" t="s">
+        <v>246</v>
+      </c>
+      <c r="H20" s="69" t="s">
+        <v>248</v>
+      </c>
+      <c r="I20" s="70" t="s">
+        <v>39</v>
+      </c>
+      <c r="J20" s="94" t="s">
         <v>216</v>
       </c>
-      <c r="H20" s="80" t="s">
-        <v>217</v>
-      </c>
-      <c r="I20" s="81" t="s">
-        <v>39</v>
-      </c>
-      <c r="J20" s="82" t="s">
-        <v>218</v>
-      </c>
-      <c r="K20" s="82">
+      <c r="K20" s="68">
+        <v>20</v>
+      </c>
+      <c r="L20" s="99">
+        <v>2</v>
+      </c>
+      <c r="M20" s="72">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L20" s="83">
-        <v>1</v>
-      </c>
-      <c r="M20" s="83">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N20" s="199" t="s">
+      <c r="N20" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="O20" s="84">
-        <v>0.10299999999999999</v>
-      </c>
-      <c r="P20" s="188">
+      <c r="O20" s="73">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="P20" s="130">
         <f t="shared" si="1"/>
-        <v>1.03</v>
+        <v>0.154</v>
       </c>
       <c r="Q20" s="16"/>
       <c r="R20" s="17"/>
       <c r="S20" s="11"/>
     </row>
-    <row r="21" spans="1:19" ht="15.75" thickBot="1">
+    <row r="21" spans="1:19" ht="26.25" thickBot="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="136" t="s">
+      <c r="B21" s="112" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="197" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="170" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="125" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="125" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="183" t="s">
+        <v>146</v>
+      </c>
+      <c r="I21" s="137" t="s">
+        <v>147</v>
+      </c>
+      <c r="J21" s="188" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="188">
+        <v>42</v>
+      </c>
+      <c r="L21" s="52">
+        <v>8</v>
+      </c>
+      <c r="M21" s="52">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="N21" s="189" t="s">
+        <v>155</v>
+      </c>
+      <c r="O21" s="127">
+        <v>3.68</v>
+      </c>
+      <c r="P21" s="54">
+        <f t="shared" si="1"/>
+        <v>154.56</v>
+      </c>
+      <c r="Q21" s="190"/>
+      <c r="R21" s="206"/>
+      <c r="S21" s="11"/>
+    </row>
+    <row r="22" spans="1:19" ht="26.25" thickBot="1">
+      <c r="A22" s="6">
+        <v>20</v>
+      </c>
+      <c r="B22" s="111" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="115" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="171" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="89" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="89" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="H22" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="J22" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="193">
+        <v>10</v>
+      </c>
+      <c r="L22" s="133">
+        <v>1</v>
+      </c>
+      <c r="M22" s="133">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N22" s="194" t="s">
+        <v>16</v>
+      </c>
+      <c r="O22" s="60">
+        <v>6.0600000000000001E-2</v>
+      </c>
+      <c r="P22" s="134">
+        <f t="shared" si="1"/>
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="11"/>
+    </row>
+    <row r="23" spans="1:19" ht="26.25" thickBot="1">
+      <c r="A23" s="6">
+        <v>21</v>
+      </c>
+      <c r="B23" s="164" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="90" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="91" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="91" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="91" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>126</v>
+      </c>
+      <c r="I23" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="64">
+        <v>7</v>
+      </c>
+      <c r="L23" s="65">
+        <v>1</v>
+      </c>
+      <c r="M23" s="65">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N23" s="92" t="s">
+        <v>16</v>
+      </c>
+      <c r="O23" s="66">
+        <v>0.25650000000000001</v>
+      </c>
+      <c r="P23" s="67">
+        <f>O23*K23</f>
+        <v>1.7955000000000001</v>
+      </c>
+      <c r="Q23" s="18"/>
+      <c r="R23" s="36"/>
+      <c r="S23" s="11"/>
+    </row>
+    <row r="24" spans="1:19" ht="26.25" thickBot="1">
+      <c r="A24" s="6">
+        <v>22</v>
+      </c>
+      <c r="B24" s="163"/>
+      <c r="C24" s="97" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="166" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="84" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="84" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" s="55" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="J24" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="51">
+        <v>7</v>
+      </c>
+      <c r="L24" s="119">
+        <v>2</v>
+      </c>
+      <c r="M24" s="119">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N24" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="O24" s="53">
+        <v>0.1215</v>
+      </c>
+      <c r="P24" s="120">
+        <f t="shared" si="1"/>
+        <v>0.85050000000000003</v>
+      </c>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="11"/>
+    </row>
+    <row r="25" spans="1:19" ht="26.25" thickBot="1">
+      <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="C21" s="193" t="s">
+      <c r="B25" s="165"/>
+      <c r="C25" s="93" t="s">
+        <v>172</v>
+      </c>
+      <c r="D25" s="167" t="s">
+        <v>173</v>
+      </c>
+      <c r="E25" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="94" t="s">
+        <v>174</v>
+      </c>
+      <c r="G25" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="H25" s="69" t="s">
+        <v>215</v>
+      </c>
+      <c r="I25" s="70" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" s="71" t="s">
+        <v>216</v>
+      </c>
+      <c r="K25" s="71">
+        <v>10</v>
+      </c>
+      <c r="L25" s="72">
+        <v>1</v>
+      </c>
+      <c r="M25" s="72">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N25" s="140" t="s">
+        <v>16</v>
+      </c>
+      <c r="O25" s="73">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="P25" s="130">
+        <f t="shared" si="1"/>
+        <v>1.03</v>
+      </c>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="11"/>
+    </row>
+    <row r="26" spans="1:19" ht="15.75" thickBot="1">
+      <c r="A26" s="6">
+        <v>24</v>
+      </c>
+      <c r="B26" s="163" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="135" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="194" t="s">
-        <v>176</v>
-      </c>
-      <c r="E21" s="182" t="s">
+      <c r="D26" s="170" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="195" t="s">
+      <c r="F26" s="136" t="s">
         <v>85</v>
       </c>
-      <c r="G21" s="50" t="s">
+      <c r="G26" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="H21" s="183" t="s">
+      <c r="H26" s="126" t="s">
         <v>130</v>
       </c>
-      <c r="I21" s="196" t="s">
+      <c r="I26" s="137" t="s">
         <v>129</v>
       </c>
-      <c r="J21" s="182" t="s">
+      <c r="J26" s="125" t="s">
         <v>89</v>
       </c>
-      <c r="K21" s="197">
+      <c r="K26" s="138">
         <v>100</v>
       </c>
-      <c r="L21" s="197">
+      <c r="L26" s="138">
         <v>3</v>
       </c>
-      <c r="M21" s="54">
+      <c r="M26" s="52">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="N21" s="198" t="s">
+      <c r="N26" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="O21" s="184">
+      <c r="O26" s="127">
         <v>1E-3</v>
       </c>
-      <c r="P21" s="56">
+      <c r="P26" s="54">
         <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
-      <c r="Q21" s="185"/>
-      <c r="R21" s="189"/>
-      <c r="S21" s="11"/>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="6">
-        <v>20</v>
-      </c>
-      <c r="B22" s="136"/>
-      <c r="C22" s="110" t="s">
-        <v>177</v>
-      </c>
-      <c r="D22" s="140" t="s">
-        <v>178</v>
-      </c>
-      <c r="E22" s="95" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" s="95" t="s">
-        <v>179</v>
-      </c>
-      <c r="G22" s="57" t="s">
-        <v>115</v>
-      </c>
-      <c r="H22" s="51" t="s">
-        <v>219</v>
-      </c>
-      <c r="I22" s="157" t="s">
-        <v>40</v>
-      </c>
-      <c r="J22" s="95" t="s">
-        <v>183</v>
-      </c>
-      <c r="K22" s="158">
-        <v>100</v>
-      </c>
-      <c r="L22" s="158">
-        <v>1</v>
-      </c>
-      <c r="M22" s="176">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N22" s="179" t="s">
-        <v>16</v>
-      </c>
-      <c r="O22" s="55">
-        <v>3.7000000000000002E-3</v>
-      </c>
-      <c r="P22" s="177">
-        <f t="shared" si="1"/>
-        <v>0.37</v>
-      </c>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="15"/>
-      <c r="S22" s="11"/>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A23" s="6">
-        <v>21</v>
-      </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="110" t="s">
-        <v>180</v>
-      </c>
-      <c r="D23" s="140" t="s">
-        <v>181</v>
-      </c>
-      <c r="E23" s="95" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="95" t="s">
-        <v>182</v>
-      </c>
-      <c r="G23" s="57" t="s">
-        <v>115</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>220</v>
-      </c>
-      <c r="I23" s="157" t="s">
-        <v>40</v>
-      </c>
-      <c r="J23" s="95" t="s">
-        <v>184</v>
-      </c>
-      <c r="K23" s="158">
-        <v>100</v>
-      </c>
-      <c r="L23" s="158">
-        <v>1</v>
-      </c>
-      <c r="M23" s="176">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N23" s="179" t="s">
-        <v>16</v>
-      </c>
-      <c r="O23" s="55">
-        <v>1.5E-3</v>
-      </c>
-      <c r="P23" s="177">
-        <f t="shared" si="1"/>
-        <v>0.15</v>
-      </c>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="11"/>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A24" s="6">
-        <v>22</v>
-      </c>
-      <c r="B24" s="136"/>
-      <c r="C24" s="160" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="141" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" s="100" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="100" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="H24" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="I24" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="J24" s="100" t="s">
-        <v>25</v>
-      </c>
-      <c r="K24" s="205">
-        <v>100</v>
-      </c>
-      <c r="L24" s="205">
-        <v>1</v>
-      </c>
-      <c r="M24" s="191">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N24" s="206" t="s">
-        <v>16</v>
-      </c>
-      <c r="O24" s="63">
-        <v>1.4E-3</v>
-      </c>
-      <c r="P24" s="192">
-        <f t="shared" si="1"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="32"/>
-      <c r="S24" s="11"/>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A25" s="6">
-        <v>23</v>
-      </c>
-      <c r="B25" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="C25" s="103" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="151" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" s="90" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" s="90" t="s">
-        <v>93</v>
-      </c>
-      <c r="G25" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="I25" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="J25" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="K25" s="46">
-        <v>11</v>
-      </c>
-      <c r="L25" s="92">
-        <v>2</v>
-      </c>
-      <c r="M25" s="47">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="N25" s="109" t="s">
-        <v>16</v>
-      </c>
-      <c r="O25" s="48">
-        <v>0.44729999999999998</v>
-      </c>
-      <c r="P25" s="49">
-        <f t="shared" si="1"/>
-        <v>4.9203000000000001</v>
-      </c>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="13"/>
-      <c r="S25" s="11"/>
-    </row>
-    <row r="26" spans="1:19" ht="26.25" thickBot="1">
-      <c r="A26" s="6">
-        <v>24</v>
-      </c>
-      <c r="B26" s="136"/>
-      <c r="C26" s="110" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="140" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="95" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" s="95" t="s">
-        <v>96</v>
-      </c>
-      <c r="G26" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="H26" s="52" t="s">
-        <v>135</v>
-      </c>
-      <c r="I26" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="J26" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="K26" s="52">
-        <v>6</v>
-      </c>
-      <c r="L26" s="97">
-        <v>1</v>
-      </c>
-      <c r="M26" s="176">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N26" s="99" t="s">
-        <v>16</v>
-      </c>
-      <c r="O26" s="55">
-        <v>0.53200000000000003</v>
-      </c>
-      <c r="P26" s="177">
-        <f t="shared" si="1"/>
-        <v>3.1920000000000002</v>
-      </c>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="15"/>
+      <c r="Q26" s="128"/>
+      <c r="R26" s="131"/>
       <c r="S26" s="11"/>
     </row>
     <row r="27" spans="1:19" ht="15.75" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="136"/>
-      <c r="C27" s="110" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" s="140" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="95" t="s">
-        <v>98</v>
-      </c>
-      <c r="F27" s="95" t="s">
-        <v>99</v>
-      </c>
-      <c r="G27" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="J27" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="K27" s="57">
-        <v>6</v>
-      </c>
-      <c r="L27" s="97">
+      <c r="B27" s="163"/>
+      <c r="C27" s="97" t="s">
+        <v>176</v>
+      </c>
+      <c r="D27" s="166" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" s="84" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="84" t="s">
+        <v>178</v>
+      </c>
+      <c r="G27" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="I27" s="113" t="s">
+        <v>40</v>
+      </c>
+      <c r="J27" s="84" t="s">
+        <v>182</v>
+      </c>
+      <c r="K27" s="114">
+        <v>100</v>
+      </c>
+      <c r="L27" s="114">
         <v>1</v>
       </c>
-      <c r="M27" s="176">
+      <c r="M27" s="119">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N27" s="111" t="s">
-        <v>136</v>
-      </c>
-      <c r="O27" s="85">
-        <v>8</v>
-      </c>
-      <c r="P27" s="177">
+      <c r="N27" s="122" t="s">
+        <v>16</v>
+      </c>
+      <c r="O27" s="53">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="P27" s="120">
         <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-      <c r="Q27" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="R27" s="33"/>
+        <v>0.37</v>
+      </c>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="15"/>
       <c r="S27" s="11"/>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="136"/>
-      <c r="C28" s="117" t="s">
+      <c r="B28" s="163"/>
+      <c r="C28" s="97" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" s="166" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" s="84" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="84" t="s">
+        <v>181</v>
+      </c>
+      <c r="G28" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="H28" s="49" t="s">
+        <v>218</v>
+      </c>
+      <c r="I28" s="113" t="s">
+        <v>40</v>
+      </c>
+      <c r="J28" s="84" t="s">
+        <v>183</v>
+      </c>
+      <c r="K28" s="114">
         <v>100</v>
       </c>
-      <c r="D28" s="159" t="s">
-        <v>101</v>
-      </c>
-      <c r="E28" s="118" t="s">
-        <v>138</v>
-      </c>
-      <c r="F28" s="118" t="s">
-        <v>102</v>
-      </c>
-      <c r="G28" s="119" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28" s="119" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="118" t="s">
-        <v>39</v>
-      </c>
-      <c r="J28" s="118" t="s">
-        <v>22</v>
-      </c>
-      <c r="K28" s="119">
-        <v>11</v>
-      </c>
-      <c r="L28" s="120">
-        <v>2</v>
-      </c>
-      <c r="M28" s="120">
+      <c r="L28" s="114">
+        <v>1</v>
+      </c>
+      <c r="M28" s="119">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="N28" s="121" t="s">
-        <v>155</v>
-      </c>
-      <c r="O28" s="180">
-        <v>10.18</v>
-      </c>
-      <c r="P28" s="181">
+        <v>5</v>
+      </c>
+      <c r="N28" s="122" t="s">
+        <v>16</v>
+      </c>
+      <c r="O28" s="53">
+        <v>1.5E-3</v>
+      </c>
+      <c r="P28" s="120">
         <f t="shared" si="1"/>
-        <v>111.97999999999999</v>
-      </c>
-      <c r="Q28" s="122"/>
-      <c r="R28" s="123"/>
+        <v>0.15</v>
+      </c>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="15"/>
       <c r="S28" s="11"/>
     </row>
     <row r="29" spans="1:19" ht="15.75" thickBot="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="136"/>
-      <c r="C29" s="110" t="s">
-        <v>186</v>
-      </c>
-      <c r="D29" s="140" t="s">
-        <v>187</v>
-      </c>
-      <c r="E29" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="F29" s="95" t="s">
-        <v>188</v>
-      </c>
-      <c r="G29" s="57" t="s">
-        <v>222</v>
-      </c>
-      <c r="H29" s="57" t="s">
-        <v>223</v>
-      </c>
-      <c r="I29" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="J29" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="K29" s="57">
-        <v>6</v>
-      </c>
-      <c r="L29" s="97">
-        <v>1</v>
-      </c>
-      <c r="M29" s="176">
+      <c r="B29" s="163"/>
+      <c r="C29" s="97" t="s">
+        <v>249</v>
+      </c>
+      <c r="D29" s="166" t="s">
+        <v>250</v>
+      </c>
+      <c r="E29" s="84" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="84" t="s">
+        <v>251</v>
+      </c>
+      <c r="G29" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="H29" s="49" t="s">
+        <v>252</v>
+      </c>
+      <c r="I29" s="113" t="s">
+        <v>40</v>
+      </c>
+      <c r="J29" s="84" t="s">
+        <v>253</v>
+      </c>
+      <c r="K29" s="114">
+        <v>100</v>
+      </c>
+      <c r="L29" s="114">
+        <v>4</v>
+      </c>
+      <c r="M29" s="119">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N29" s="125" t="s">
+        <v>20</v>
+      </c>
+      <c r="N29" s="122" t="s">
         <v>16</v>
       </c>
-      <c r="O29" s="55">
-        <v>2.3479000000000001</v>
-      </c>
-      <c r="P29" s="177">
+      <c r="O29" s="53">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="P29" s="120">
         <f t="shared" si="1"/>
-        <v>14.087400000000001</v>
-      </c>
-      <c r="Q29" s="22"/>
+        <v>0.13</v>
+      </c>
+      <c r="Q29" s="14"/>
       <c r="R29" s="15"/>
       <c r="S29" s="11"/>
     </row>
@@ -3902,548 +3954,953 @@
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="136"/>
-      <c r="C30" s="110" t="s">
-        <v>189</v>
-      </c>
-      <c r="D30" s="140" t="s">
-        <v>190</v>
-      </c>
-      <c r="E30" s="95" t="s">
-        <v>191</v>
-      </c>
-      <c r="F30" s="95" t="s">
-        <v>192</v>
+      <c r="B30" s="163"/>
+      <c r="C30" s="115" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="171" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" s="89" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="89" t="s">
+        <v>88</v>
       </c>
       <c r="G30" s="57" t="s">
-        <v>224</v>
-      </c>
-      <c r="H30" s="57" t="s">
-        <v>225</v>
-      </c>
-      <c r="I30" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="J30" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="K30" s="57">
-        <v>6</v>
-      </c>
-      <c r="L30" s="97">
+        <v>115</v>
+      </c>
+      <c r="H30" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="I30" s="169" t="s">
+        <v>40</v>
+      </c>
+      <c r="J30" s="89" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" s="141">
+        <v>100</v>
+      </c>
+      <c r="L30" s="141">
         <v>1</v>
       </c>
-      <c r="M30" s="176">
+      <c r="M30" s="133">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N30" s="125" t="s">
+      <c r="N30" s="142" t="s">
         <v>16</v>
       </c>
-      <c r="O30" s="55">
-        <v>0.74660000000000004</v>
-      </c>
-      <c r="P30" s="177">
+      <c r="O30" s="60">
+        <v>1.4E-3</v>
+      </c>
+      <c r="P30" s="134">
         <f t="shared" si="1"/>
-        <v>4.4796000000000005</v>
-      </c>
-      <c r="Q30" s="22"/>
-      <c r="R30" s="15"/>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="31"/>
       <c r="S30" s="11"/>
     </row>
-    <row r="31" spans="1:19" ht="26.25" thickBot="1">
+    <row r="31" spans="1:19" ht="15.75" thickBot="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="137"/>
-      <c r="C31" s="106" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31" s="152" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" s="107" t="s">
-        <v>139</v>
-      </c>
-      <c r="F31" s="107" t="s">
-        <v>105</v>
-      </c>
-      <c r="G31" s="82" t="s">
-        <v>140</v>
-      </c>
-      <c r="H31" s="82" t="s">
-        <v>141</v>
-      </c>
-      <c r="I31" s="82" t="s">
+      <c r="B31" s="164" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="90" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="G31" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J31" s="82" t="s">
+      <c r="J31" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K31" s="79">
+      <c r="K31" s="44">
+        <v>11</v>
+      </c>
+      <c r="L31" s="81">
+        <v>2</v>
+      </c>
+      <c r="M31" s="45">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L31" s="112">
+      <c r="N31" s="96" t="s">
+        <v>16</v>
+      </c>
+      <c r="O31" s="46">
+        <v>0.44729999999999998</v>
+      </c>
+      <c r="P31" s="47">
+        <f t="shared" si="1"/>
+        <v>4.9203000000000001</v>
+      </c>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="11"/>
+    </row>
+    <row r="32" spans="1:19" ht="26.25" thickBot="1">
+      <c r="A32" s="6">
+        <v>30</v>
+      </c>
+      <c r="B32" s="163"/>
+      <c r="C32" s="97" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="166" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="84" t="s">
+        <v>95</v>
+      </c>
+      <c r="F32" s="84" t="s">
+        <v>96</v>
+      </c>
+      <c r="G32" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="H32" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="I32" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="J32" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K32" s="50">
+        <v>6</v>
+      </c>
+      <c r="L32" s="86">
         <v>1</v>
       </c>
-      <c r="M31" s="83">
+      <c r="M32" s="119">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N31" s="113" t="s">
+      <c r="N32" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="O31" s="84">
-        <v>5.8799999999999998E-2</v>
-      </c>
-      <c r="P31" s="188">
+      <c r="O32" s="53">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="P32" s="120">
         <f t="shared" si="1"/>
-        <v>0.58799999999999997</v>
-      </c>
-      <c r="Q31" s="23"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="11"/>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A32" s="6">
-        <v>30</v>
-      </c>
-      <c r="B32" s="135" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" s="103" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" s="151" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="F32" s="108" t="s">
-        <v>108</v>
-      </c>
-      <c r="G32" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="H32" s="47" t="s">
-        <v>143</v>
-      </c>
-      <c r="I32" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="J32" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="K32" s="86">
-        <v>50</v>
-      </c>
-      <c r="L32" s="87">
-        <v>1</v>
-      </c>
-      <c r="M32" s="47">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N32" s="114" t="s">
-        <v>16</v>
-      </c>
-      <c r="O32" s="48">
-        <v>1.5699999999999999E-2</v>
-      </c>
-      <c r="P32" s="49">
-        <f t="shared" si="1"/>
-        <v>0.78499999999999992</v>
-      </c>
-      <c r="Q32" s="24"/>
-      <c r="R32" s="13"/>
+        <v>3.1920000000000002</v>
+      </c>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="15"/>
       <c r="S32" s="11"/>
     </row>
     <row r="33" spans="1:19" ht="15.75" thickBot="1">
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="136"/>
-      <c r="C33" s="110" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" s="140" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="95" t="s">
-        <v>28</v>
-      </c>
-      <c r="F33" s="95" t="s">
-        <v>156</v>
-      </c>
-      <c r="G33" s="53" t="s">
-        <v>159</v>
-      </c>
-      <c r="H33" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="I33" s="53" t="s">
+      <c r="B33" s="163"/>
+      <c r="C33" s="97" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" s="166" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="84" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" s="84" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="J33" s="53" t="s">
+      <c r="J33" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="K33" s="53">
+      <c r="K33" s="55">
         <v>6</v>
       </c>
-      <c r="L33" s="88">
+      <c r="L33" s="86">
         <v>1</v>
       </c>
-      <c r="M33" s="176">
+      <c r="M33" s="119">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N33" s="125" t="s">
-        <v>16</v>
-      </c>
-      <c r="O33" s="85">
-        <v>0.25409999999999999</v>
-      </c>
-      <c r="P33" s="177">
+      <c r="N33" s="98" t="s">
+        <v>136</v>
+      </c>
+      <c r="O33" s="74">
+        <v>8</v>
+      </c>
+      <c r="P33" s="120">
         <f t="shared" si="1"/>
-        <v>1.5246</v>
-      </c>
-      <c r="Q33" s="28"/>
-      <c r="R33" s="15"/>
+        <v>48</v>
+      </c>
+      <c r="Q33" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="R33" s="32"/>
       <c r="S33" s="11"/>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="136"/>
-      <c r="C34" s="110" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34" s="140" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="95" t="s">
-        <v>28</v>
-      </c>
-      <c r="F34" s="115" t="s">
-        <v>110</v>
-      </c>
-      <c r="G34" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="H34" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="I34" s="53" t="s">
-        <v>150</v>
-      </c>
-      <c r="J34" s="53" t="s">
+      <c r="B34" s="163"/>
+      <c r="C34" s="103" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="172" t="s">
+        <v>101</v>
+      </c>
+      <c r="E34" s="104" t="s">
+        <v>138</v>
+      </c>
+      <c r="F34" s="104" t="s">
+        <v>102</v>
+      </c>
+      <c r="G34" s="105" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="53">
-        <v>50</v>
-      </c>
-      <c r="L34" s="88">
+      <c r="I34" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="104" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" s="105">
+        <v>11</v>
+      </c>
+      <c r="L34" s="106">
+        <v>2</v>
+      </c>
+      <c r="M34" s="106">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N34" s="107" t="s">
+        <v>155</v>
+      </c>
+      <c r="O34" s="123">
+        <v>10.18</v>
+      </c>
+      <c r="P34" s="124">
+        <f t="shared" si="1"/>
+        <v>111.97999999999999</v>
+      </c>
+      <c r="Q34" s="108"/>
+      <c r="R34" s="109"/>
+      <c r="S34" s="11"/>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" thickBot="1">
+      <c r="A35" s="6">
+        <v>33</v>
+      </c>
+      <c r="B35" s="163"/>
+      <c r="C35" s="97" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" s="166" t="s">
+        <v>185</v>
+      </c>
+      <c r="E35" s="84" t="s">
+        <v>219</v>
+      </c>
+      <c r="F35" s="84" t="s">
+        <v>186</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="I35" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="J35" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="55">
+        <v>6</v>
+      </c>
+      <c r="L35" s="86">
         <v>1</v>
       </c>
-      <c r="M34" s="176">
+      <c r="M35" s="119">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N34" s="111" t="s">
+      <c r="N35" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="O34" s="55">
+      <c r="O35" s="53">
+        <v>2.3479000000000001</v>
+      </c>
+      <c r="P35" s="120">
+        <f t="shared" si="1"/>
+        <v>14.087400000000001</v>
+      </c>
+      <c r="Q35" s="22"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="11"/>
+    </row>
+    <row r="36" spans="1:19" ht="15.75" thickBot="1">
+      <c r="A36" s="6">
+        <v>34</v>
+      </c>
+      <c r="B36" s="163"/>
+      <c r="C36" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" s="166" t="s">
+        <v>188</v>
+      </c>
+      <c r="E36" s="84" t="s">
+        <v>189</v>
+      </c>
+      <c r="F36" s="84" t="s">
+        <v>190</v>
+      </c>
+      <c r="G36" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="H36" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="I36" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="J36" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" s="55">
+        <v>6</v>
+      </c>
+      <c r="L36" s="86">
+        <v>1</v>
+      </c>
+      <c r="M36" s="119">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N36" s="110" t="s">
+        <v>16</v>
+      </c>
+      <c r="O36" s="53">
+        <v>0.74660000000000004</v>
+      </c>
+      <c r="P36" s="120">
+        <f t="shared" si="1"/>
+        <v>4.4796000000000005</v>
+      </c>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="11"/>
+    </row>
+    <row r="37" spans="1:19" ht="26.25" thickBot="1">
+      <c r="A37" s="6">
+        <v>35</v>
+      </c>
+      <c r="B37" s="165"/>
+      <c r="C37" s="93" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" s="167" t="s">
+        <v>104</v>
+      </c>
+      <c r="E37" s="94" t="s">
+        <v>139</v>
+      </c>
+      <c r="F37" s="94" t="s">
+        <v>105</v>
+      </c>
+      <c r="G37" s="71" t="s">
+        <v>140</v>
+      </c>
+      <c r="H37" s="71" t="s">
+        <v>141</v>
+      </c>
+      <c r="I37" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="K37" s="68">
+        <v>10</v>
+      </c>
+      <c r="L37" s="99">
+        <v>1</v>
+      </c>
+      <c r="M37" s="72">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N37" s="100" t="s">
+        <v>16</v>
+      </c>
+      <c r="O37" s="73">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="P37" s="130">
+        <f t="shared" si="1"/>
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="Q37" s="23"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="11"/>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" thickBot="1">
+      <c r="A38" s="6">
+        <v>36</v>
+      </c>
+      <c r="B38" s="164" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="90" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="91" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="79" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="95" t="s">
+        <v>108</v>
+      </c>
+      <c r="G38" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="H38" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="I38" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" s="75">
+        <v>50</v>
+      </c>
+      <c r="L38" s="76">
+        <v>1</v>
+      </c>
+      <c r="M38" s="45">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N38" s="101" t="s">
+        <v>16</v>
+      </c>
+      <c r="O38" s="46">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="P38" s="47">
+        <f t="shared" si="1"/>
+        <v>0.78499999999999992</v>
+      </c>
+      <c r="Q38" s="24"/>
+      <c r="R38" s="13"/>
+      <c r="S38" s="11"/>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" thickBot="1">
+      <c r="A39" s="6">
+        <v>37</v>
+      </c>
+      <c r="B39" s="163"/>
+      <c r="C39" s="97" t="s">
+        <v>157</v>
+      </c>
+      <c r="D39" s="166" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="84" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" s="84" t="s">
+        <v>156</v>
+      </c>
+      <c r="G39" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="H39" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="I39" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="J39" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" s="51">
+        <v>6</v>
+      </c>
+      <c r="L39" s="77">
+        <v>1</v>
+      </c>
+      <c r="M39" s="119">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N39" s="110" t="s">
+        <v>16</v>
+      </c>
+      <c r="O39" s="74">
+        <v>0.25409999999999999</v>
+      </c>
+      <c r="P39" s="120">
+        <f t="shared" si="1"/>
+        <v>1.5246</v>
+      </c>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="11"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" thickBot="1">
+      <c r="A40" s="6">
+        <v>38</v>
+      </c>
+      <c r="B40" s="163"/>
+      <c r="C40" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="166" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" s="84" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="102" t="s">
+        <v>110</v>
+      </c>
+      <c r="G40" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="H40" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="I40" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="J40" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" s="51">
+        <v>50</v>
+      </c>
+      <c r="L40" s="77">
+        <v>1</v>
+      </c>
+      <c r="M40" s="119">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N40" s="98" t="s">
+        <v>16</v>
+      </c>
+      <c r="O40" s="53">
         <v>1.26E-2</v>
       </c>
-      <c r="P34" s="177">
+      <c r="P40" s="120">
         <f t="shared" si="1"/>
         <v>0.63</v>
       </c>
-      <c r="Q34" s="29"/>
-      <c r="R34" s="15"/>
-      <c r="S34" s="11"/>
-    </row>
-    <row r="35" spans="1:19" ht="102.75" thickBot="1">
-      <c r="A35" s="6">
-        <v>33</v>
-      </c>
-      <c r="B35" s="137"/>
-      <c r="C35" s="215" t="s">
+      <c r="Q40" s="29"/>
+      <c r="R40" s="15"/>
+      <c r="S40" s="11"/>
+    </row>
+    <row r="41" spans="1:19" ht="115.5" thickBot="1">
+      <c r="A41" s="19">
+        <v>39</v>
+      </c>
+      <c r="B41" s="165"/>
+      <c r="C41" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="216" t="s">
-        <v>185</v>
-      </c>
-      <c r="E35" s="217" t="s">
+      <c r="D41" s="144" t="s">
+        <v>254</v>
+      </c>
+      <c r="E41" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="F35" s="217" t="s">
+      <c r="F41" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="G35" s="218" t="s">
+      <c r="G41" s="146" t="s">
         <v>146</v>
       </c>
-      <c r="H35" s="218" t="s">
+      <c r="H41" s="146" t="s">
         <v>146</v>
       </c>
-      <c r="I35" s="219" t="s">
+      <c r="I41" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="J35" s="219" t="s">
+      <c r="J41" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="K35" s="219" t="s">
+      <c r="K41" s="147" t="s">
         <v>146</v>
       </c>
-      <c r="L35" s="220">
-        <v>42</v>
-      </c>
-      <c r="M35" s="221">
+      <c r="L41" s="148">
+        <v>53</v>
+      </c>
+      <c r="M41" s="149">
         <f t="shared" si="0"/>
-        <v>210</v>
-      </c>
-      <c r="N35" s="218" t="s">
+        <v>265</v>
+      </c>
+      <c r="N41" s="146" t="s">
         <v>146</v>
       </c>
-      <c r="O35" s="219" t="s">
+      <c r="O41" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="P35" s="219" t="s">
+      <c r="P41" s="147" t="s">
         <v>146</v>
       </c>
-      <c r="Q35" s="222" t="s">
+      <c r="Q41" s="150" t="s">
         <v>151</v>
       </c>
-      <c r="R35" s="223"/>
-      <c r="S35" s="11"/>
-    </row>
-    <row r="36" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A36" s="19">
-        <v>34</v>
-      </c>
-      <c r="B36" s="161" t="s">
+      <c r="R41" s="151"/>
+      <c r="S41" s="11"/>
+    </row>
+    <row r="42" spans="1:19" ht="15.75" thickBot="1">
+      <c r="A42" s="6">
+        <v>40</v>
+      </c>
+      <c r="B42" s="209" t="s">
         <v>153</v>
       </c>
-      <c r="C36" s="207" t="s">
+      <c r="C42" s="210" t="s">
+        <v>255</v>
+      </c>
+      <c r="D42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="G42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="H42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="I42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="J42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="K42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="L42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="M42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="N42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="O42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="P42" s="173" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q42" s="174" t="s">
+        <v>151</v>
+      </c>
+      <c r="R42" s="175"/>
+      <c r="S42" s="11"/>
+    </row>
+    <row r="43" spans="1:19" ht="15.75" thickBot="1">
+      <c r="A43" s="6">
+        <v>41</v>
+      </c>
+      <c r="B43" s="168"/>
+      <c r="C43" s="211" t="s">
         <v>154</v>
       </c>
-      <c r="D36" s="208" t="s">
+      <c r="D43" s="212" t="s">
         <v>40</v>
       </c>
-      <c r="E36" s="208" t="s">
+      <c r="E43" s="212" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="209" t="s">
+      <c r="F43" s="213" t="s">
         <v>154</v>
       </c>
-      <c r="G36" s="208" t="s">
+      <c r="G43" s="212" t="s">
         <v>40</v>
       </c>
-      <c r="H36" s="208" t="s">
+      <c r="H43" s="212" t="s">
         <v>40</v>
       </c>
-      <c r="I36" s="208" t="s">
+      <c r="I43" s="212" t="s">
         <v>40</v>
       </c>
-      <c r="J36" s="208" t="s">
+      <c r="J43" s="212" t="s">
         <v>40</v>
       </c>
-      <c r="K36" s="208" t="s">
+      <c r="K43" s="212" t="s">
         <v>40</v>
       </c>
-      <c r="L36" s="210">
+      <c r="L43" s="176">
         <v>1</v>
       </c>
-      <c r="M36" s="210">
-        <f t="shared" si="0"/>
+      <c r="M43" s="176">
+        <f t="shared" ref="M43" si="2">L43*5</f>
         <v>5</v>
       </c>
-      <c r="N36" s="211"/>
-      <c r="O36" s="212"/>
-      <c r="P36" s="212"/>
-      <c r="Q36" s="213"/>
-      <c r="R36" s="214"/>
-      <c r="S36" s="11"/>
-    </row>
-    <row r="37" spans="1:19" ht="15.75">
-      <c r="A37" s="1"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="173" t="s">
+      <c r="N43" s="177" t="s">
+        <v>256</v>
+      </c>
+      <c r="O43" s="178">
+        <v>3.35</v>
+      </c>
+      <c r="P43" s="179">
+        <f>O43*M43</f>
+        <v>16.75</v>
+      </c>
+      <c r="Q43" s="150" t="s">
+        <v>151</v>
+      </c>
+      <c r="R43" s="214"/>
+      <c r="S43" s="11"/>
+    </row>
+    <row r="44" spans="1:19" ht="15.75">
+      <c r="A44" s="1"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="159" t="s">
         <v>37</v>
       </c>
-      <c r="M37" s="174"/>
-      <c r="N37" s="174"/>
-      <c r="O37" s="21"/>
-      <c r="P37" s="175">
-        <f>SUM(P3:P36)</f>
-        <v>358.21090000000009</v>
-      </c>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="7"/>
-      <c r="S37" s="11"/>
-    </row>
-    <row r="38" spans="1:19" ht="16.5" thickBot="1">
-      <c r="A38" s="1"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="133" t="s">
+      <c r="M44" s="160"/>
+      <c r="N44" s="160"/>
+      <c r="O44" s="21"/>
+      <c r="P44" s="118">
+        <f>SUM(P3:P43)</f>
+        <v>378.55090000000007</v>
+      </c>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="7"/>
+      <c r="S44" s="11"/>
+    </row>
+    <row r="45" spans="1:19" ht="16.5" thickBot="1">
+      <c r="A45" s="1"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="M38" s="134"/>
-      <c r="N38" s="134"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="42">
-        <f>P37/5</f>
-        <v>71.642180000000025</v>
-      </c>
-      <c r="Q38" s="7"/>
-      <c r="R38" s="7"/>
-      <c r="S38" s="11"/>
-    </row>
-    <row r="39" spans="1:19" ht="15.75">
-      <c r="A39" s="1"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="126" t="s">
+      <c r="M45" s="162"/>
+      <c r="N45" s="162"/>
+      <c r="O45" s="37"/>
+      <c r="P45" s="40">
+        <f>P44/5</f>
+        <v>75.710180000000008</v>
+      </c>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="11"/>
+    </row>
+    <row r="46" spans="1:19" ht="15.75">
+      <c r="A46" s="1"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="33"/>
+      <c r="M46" s="152" t="s">
         <v>149</v>
       </c>
-      <c r="N39" s="127"/>
-      <c r="O39" s="35"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="7"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="11"/>
-    </row>
-    <row r="40" spans="1:19" ht="16.5" thickBot="1">
-      <c r="A40" s="1"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="M40" s="128" t="s">
+      <c r="N46" s="153"/>
+      <c r="O46" s="34"/>
+      <c r="P46" s="39"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="11"/>
+    </row>
+    <row r="47" spans="1:19" ht="15.75">
+      <c r="A47" s="1"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="180" t="s">
+        <v>257</v>
+      </c>
+      <c r="N47" s="181"/>
+      <c r="O47" s="34"/>
+      <c r="P47" s="182">
+        <v>213.77</v>
+      </c>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="11"/>
+    </row>
+    <row r="48" spans="1:19" ht="16.5" thickBot="1">
+      <c r="A48" s="1"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="M48" s="154" t="s">
         <v>43</v>
       </c>
-      <c r="N40" s="129"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40" t="e">
-        <f>#REF!+P37</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R40" s="11"/>
-      <c r="S40" s="11"/>
-    </row>
-    <row r="41" spans="1:19">
-      <c r="A41" s="1"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="M41" s="20"/>
-      <c r="R41" s="11"/>
-      <c r="S41" s="11"/>
-    </row>
-    <row r="42" spans="1:19">
-      <c r="A42" s="1"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="R42" s="11"/>
-      <c r="S42" s="11"/>
-    </row>
-    <row r="43" spans="1:19">
-      <c r="A43" s="1"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="R43" s="11"/>
-      <c r="S43" s="11"/>
-    </row>
-    <row r="44" spans="1:19">
-      <c r="A44" s="1"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="R44" s="11"/>
-      <c r="S44" s="11"/>
-    </row>
-    <row r="45" spans="1:19">
-      <c r="A45" s="1"/>
-      <c r="R45" s="11"/>
-      <c r="S45" s="11"/>
-    </row>
-    <row r="46" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="R46" s="11"/>
-      <c r="S46" s="11"/>
-    </row>
-    <row r="47" spans="1:19">
-      <c r="A47" s="1"/>
-      <c r="R47" s="11"/>
-      <c r="S47" s="11"/>
-    </row>
-    <row r="48" spans="1:19">
-      <c r="A48" s="1"/>
+      <c r="N48" s="155"/>
+      <c r="O48" s="37"/>
+      <c r="P48" s="38"/>
       <c r="R48" s="11"/>
       <c r="S48" s="11"/>
     </row>
     <row r="49" spans="1:19">
       <c r="A49" s="1"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="M49" s="20"/>
       <c r="R49" s="11"/>
       <c r="S49" s="11"/>
     </row>
     <row r="50" spans="1:19">
       <c r="A50" s="1"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="I50" s="2"/>
       <c r="R50" s="11"/>
       <c r="S50" s="11"/>
     </row>
     <row r="51" spans="1:19">
       <c r="A51" s="1"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="I51" s="2"/>
       <c r="R51" s="11"/>
       <c r="S51" s="11"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="H52" s="9"/>
-      <c r="Q52" s="10"/>
+      <c r="A52" s="1"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="R52" s="11"/>
+      <c r="S52" s="11"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="H53" s="9"/>
-      <c r="Q53" s="10"/>
+      <c r="A53" s="1"/>
+      <c r="R53" s="11"/>
+      <c r="S53" s="11"/>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A54" s="1"/>
+      <c r="R54" s="11"/>
+      <c r="S54" s="11"/>
+    </row>
+    <row r="55" spans="1:19">
+      <c r="A55" s="1"/>
+      <c r="R55" s="11"/>
+      <c r="S55" s="11"/>
+    </row>
+    <row r="56" spans="1:19">
+      <c r="A56" s="1"/>
+      <c r="R56" s="11"/>
+      <c r="S56" s="11"/>
+    </row>
+    <row r="57" spans="1:19">
+      <c r="A57" s="1"/>
+      <c r="R57" s="11"/>
+      <c r="S57" s="11"/>
+    </row>
+    <row r="58" spans="1:19">
+      <c r="A58" s="1"/>
+      <c r="R58" s="11"/>
+      <c r="S58" s="11"/>
+    </row>
+    <row r="59" spans="1:19">
+      <c r="A59" s="1"/>
+      <c r="R59" s="11"/>
+      <c r="S59" s="11"/>
+    </row>
+    <row r="60" spans="1:19">
+      <c r="H60" s="9"/>
+      <c r="Q60" s="10"/>
+    </row>
+    <row r="61" spans="1:19">
+      <c r="H61" s="9"/>
+      <c r="Q61" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
+  <mergeCells count="14">
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="M48:N48"/>
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="B25:B31"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B3:B13"/>
+    <mergeCell ref="L44:N44"/>
+    <mergeCell ref="L45:N45"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="B31:B37"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B3:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="M47:N47"/>
     <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B42:B43"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="Q33">
-    <cfRule type="dataBar" priority="16">
+  <conditionalFormatting sqref="Q39">
+    <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4457,7 +4914,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:L8">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4469,7 +4926,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N5">
-    <cfRule type="dataBar" priority="13">
+    <cfRule type="dataBar" priority="16">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4482,8 +4939,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N10:N15">
-    <cfRule type="dataBar" priority="12">
+  <conditionalFormatting sqref="N10:N20">
+    <cfRule type="dataBar" priority="15">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4496,8 +4953,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P38:P39">
-    <cfRule type="dataBar" priority="28">
+  <conditionalFormatting sqref="P45:P46">
+    <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4510,19 +4967,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L25:M36 L9:L20 M3:M36">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:M36">
+  <conditionalFormatting sqref="L31:M41 L9:L25 M3:M41">
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -4534,8 +4979,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P36">
-    <cfRule type="dataBar" priority="34">
+  <conditionalFormatting sqref="L3:M41">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3:P41">
+    <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4548,8 +5005,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K35">
-    <cfRule type="dataBar" priority="1">
+  <conditionalFormatting sqref="K41">
+    <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4558,6 +5015,44 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{193AFC57-9059-4DAB-9E2A-67F7DD9723ED}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L43:M43">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L43:M43">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P43">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{19A41A86-C9BB-4A96-AA11-2BBEAF826782}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4571,32 +5066,38 @@
     <hyperlink ref="N9" r:id="rId6" xr:uid="{F5D2937B-2705-425B-A920-F69EE337A9AA}"/>
     <hyperlink ref="N10" r:id="rId7" xr:uid="{23650E7E-1F91-465B-A508-B3E81A5A29DB}"/>
     <hyperlink ref="N11" r:id="rId8" xr:uid="{A3FA0792-9C1C-4B11-8EC7-D8950B40778A}"/>
-    <hyperlink ref="N17" r:id="rId9" xr:uid="{9306F7E1-9FA0-45C1-9226-A5EFFE620B9F}"/>
-    <hyperlink ref="N18" r:id="rId10" xr:uid="{6C2F24FA-F4C6-4765-90C1-BBDF944038A7}"/>
-    <hyperlink ref="N19" r:id="rId11" xr:uid="{834B4123-1D60-4B34-B015-5E7BBC8F47AF}"/>
-    <hyperlink ref="N21" r:id="rId12" xr:uid="{1D1A071F-2A3D-4FA1-937C-5E9315A2DAC9}"/>
-    <hyperlink ref="N24" r:id="rId13" xr:uid="{1ECC2B27-3B6B-4070-A52B-CBF10AA116AF}"/>
-    <hyperlink ref="N25" r:id="rId14" xr:uid="{BFDF2136-290A-40AE-829A-CE2FE24D8034}"/>
-    <hyperlink ref="N26" r:id="rId15" xr:uid="{E71028CE-6136-4648-ABFC-ABDBCFA60DB5}"/>
-    <hyperlink ref="N31" r:id="rId16" xr:uid="{8E22EBA9-5C52-408B-A65B-4F115F1CD0F7}"/>
-    <hyperlink ref="N32" r:id="rId17" xr:uid="{0A7E773D-5A3D-486C-84CA-8D29060909A3}"/>
-    <hyperlink ref="N34" r:id="rId18" xr:uid="{79B90123-86F4-4C7F-BE0B-E5B7C590F601}"/>
-    <hyperlink ref="N16" r:id="rId19" display="Aliexpress" xr:uid="{D571A1A4-A3B8-476C-81AA-A10E0576C945}"/>
-    <hyperlink ref="N33" r:id="rId20" xr:uid="{552B4167-57FF-43F1-B0A5-FDF3A29237A4}"/>
+    <hyperlink ref="N22" r:id="rId9" xr:uid="{9306F7E1-9FA0-45C1-9226-A5EFFE620B9F}"/>
+    <hyperlink ref="N23" r:id="rId10" xr:uid="{6C2F24FA-F4C6-4765-90C1-BBDF944038A7}"/>
+    <hyperlink ref="N24" r:id="rId11" xr:uid="{834B4123-1D60-4B34-B015-5E7BBC8F47AF}"/>
+    <hyperlink ref="N26" r:id="rId12" xr:uid="{1D1A071F-2A3D-4FA1-937C-5E9315A2DAC9}"/>
+    <hyperlink ref="N30" r:id="rId13" xr:uid="{1ECC2B27-3B6B-4070-A52B-CBF10AA116AF}"/>
+    <hyperlink ref="N31" r:id="rId14" xr:uid="{BFDF2136-290A-40AE-829A-CE2FE24D8034}"/>
+    <hyperlink ref="N32" r:id="rId15" xr:uid="{E71028CE-6136-4648-ABFC-ABDBCFA60DB5}"/>
+    <hyperlink ref="N37" r:id="rId16" xr:uid="{8E22EBA9-5C52-408B-A65B-4F115F1CD0F7}"/>
+    <hyperlink ref="N38" r:id="rId17" xr:uid="{0A7E773D-5A3D-486C-84CA-8D29060909A3}"/>
+    <hyperlink ref="N40" r:id="rId18" xr:uid="{79B90123-86F4-4C7F-BE0B-E5B7C590F601}"/>
+    <hyperlink ref="N21" r:id="rId19" display="Aliexpress" xr:uid="{D571A1A4-A3B8-476C-81AA-A10E0576C945}"/>
+    <hyperlink ref="N39" r:id="rId20" xr:uid="{552B4167-57FF-43F1-B0A5-FDF3A29237A4}"/>
     <hyperlink ref="N7" r:id="rId21" xr:uid="{6FBFF76E-B622-4D29-A447-7C6E26828E4F}"/>
     <hyperlink ref="N12" r:id="rId22" xr:uid="{1242BC39-221F-4021-953C-3FCDA7A5753C}"/>
     <hyperlink ref="N13" r:id="rId23" xr:uid="{96270715-E02B-41B7-B021-EDD143E9B86E}"/>
-    <hyperlink ref="N14" r:id="rId24" xr:uid="{9B63197A-770E-4944-B769-AA91C9283ECE}"/>
-    <hyperlink ref="N15" r:id="rId25" xr:uid="{9BCD60A7-30C2-4172-B089-A68B6513C693}"/>
-    <hyperlink ref="N20" r:id="rId26" xr:uid="{B47CC2C3-43E3-4A0C-8766-540A57D9BE72}"/>
-    <hyperlink ref="N22" r:id="rId27" xr:uid="{C514E8E3-59DE-4B44-BBBE-97387454193F}"/>
-    <hyperlink ref="N23" r:id="rId28" xr:uid="{CC730C2B-3995-4162-BE6B-30851128B6A0}"/>
-    <hyperlink ref="N29" r:id="rId29" xr:uid="{9108529D-C5AF-49DE-B1AA-F619710C5B08}"/>
-    <hyperlink ref="N30" r:id="rId30" xr:uid="{31C7B57C-378C-4F81-AADD-6D3587D8A480}"/>
-    <hyperlink ref="N27" r:id="rId31" xr:uid="{600C5A90-1D13-491E-82D2-49A3F9B676E0}"/>
+    <hyperlink ref="N16" r:id="rId24" xr:uid="{9B63197A-770E-4944-B769-AA91C9283ECE}"/>
+    <hyperlink ref="N18" r:id="rId25" xr:uid="{9BCD60A7-30C2-4172-B089-A68B6513C693}"/>
+    <hyperlink ref="N25" r:id="rId26" xr:uid="{B47CC2C3-43E3-4A0C-8766-540A57D9BE72}"/>
+    <hyperlink ref="N27" r:id="rId27" xr:uid="{C514E8E3-59DE-4B44-BBBE-97387454193F}"/>
+    <hyperlink ref="N28" r:id="rId28" xr:uid="{CC730C2B-3995-4162-BE6B-30851128B6A0}"/>
+    <hyperlink ref="N35" r:id="rId29" xr:uid="{9108529D-C5AF-49DE-B1AA-F619710C5B08}"/>
+    <hyperlink ref="N36" r:id="rId30" xr:uid="{31C7B57C-378C-4F81-AADD-6D3587D8A480}"/>
+    <hyperlink ref="N33" r:id="rId31" xr:uid="{600C5A90-1D13-491E-82D2-49A3F9B676E0}"/>
+    <hyperlink ref="N14" r:id="rId32" xr:uid="{44409B7B-710F-4F54-A7F0-477BEA0AFE5F}"/>
+    <hyperlink ref="N15" r:id="rId33" xr:uid="{89198C26-8FB1-4B6B-AE7B-FFAE1D3733A8}"/>
+    <hyperlink ref="N17" r:id="rId34" xr:uid="{EC86EEC1-808E-4C17-B0CB-1E879CDB66DD}"/>
+    <hyperlink ref="N19" r:id="rId35" xr:uid="{2322511E-46DE-4717-9728-D93822E1A6A3}"/>
+    <hyperlink ref="N20" r:id="rId36" xr:uid="{2BCC81E2-819B-49BB-9670-D8361D1C41A8}"/>
+    <hyperlink ref="N29" r:id="rId37" xr:uid="{888359C9-25FD-4ECA-BFAD-B6548ECFC19D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId32"/>
+  <pageSetup orientation="portrait" r:id="rId38"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -4611,7 +5112,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>Q33</xm:sqref>
+          <xm:sqref>Q39</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{73D72061-44BE-43BF-B86A-016273A3FADD}">
@@ -4637,7 +5138,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N10:N15</xm:sqref>
+          <xm:sqref>N10:N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{A8943134-F8F0-4DF3-A9A0-86442E65814B}">
@@ -4650,7 +5151,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P38:P39</xm:sqref>
+          <xm:sqref>P45:P46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{70CE0387-EDB2-443C-842F-1D5EE6E70AF7}">
@@ -4663,7 +5164,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P3:P36</xm:sqref>
+          <xm:sqref>P3:P41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{193AFC57-9059-4DAB-9E2A-67F7DD9723ED}">
@@ -4676,7 +5177,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>K35</xm:sqref>
+          <xm:sqref>K41</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{19A41A86-C9BB-4A96-AA11-2BBEAF826782}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P43</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
